--- a/李明学的大A/Peace.xlsx
+++ b/李明学的大A/Peace.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" tabRatio="482" firstSheet="2" activeTab="2"/>
+    <workbookView windowWidth="18350" windowHeight="17680" tabRatio="482" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="每日必读" sheetId="9" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="444">
   <si>
     <t>主题</t>
   </si>
@@ -1091,6 +1091,12 @@
   </si>
   <si>
     <t>2.61%(炸板)</t>
+  </si>
+  <si>
+    <t>天元股份</t>
+  </si>
+  <si>
+    <t>大智慧</t>
   </si>
   <si>
     <t>宝泰隆</t>
@@ -30321,7 +30327,9 @@
       <c r="G273" s="176">
         <v>-0.0391</v>
       </c>
-      <c r="H273" s="176"/>
+      <c r="H273" s="176">
+        <v>-0.0048</v>
+      </c>
       <c r="I273" s="33"/>
       <c r="J273" s="33"/>
       <c r="K273" s="33"/>
@@ -30360,8 +30368,12 @@
       <c r="F274" s="41" t="s">
         <v>92</v>
       </c>
-      <c r="G274" s="176"/>
-      <c r="H274" s="176"/>
+      <c r="G274" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="H274" s="176">
+        <v>-0.0625</v>
+      </c>
       <c r="I274" s="33"/>
       <c r="J274" s="33"/>
       <c r="K274" s="33"/>
@@ -30417,9 +30429,15 @@
       <c r="D276" s="42" t="s">
         <v>314</v>
       </c>
-      <c r="E276" s="174"/>
-      <c r="F276" s="32"/>
-      <c r="G276" s="33"/>
+      <c r="E276" s="174">
+        <v>0.0271</v>
+      </c>
+      <c r="F276" s="168">
+        <v>-0.0806</v>
+      </c>
+      <c r="G276" s="169">
+        <v>0.0067</v>
+      </c>
       <c r="H276" s="33"/>
       <c r="I276" s="33"/>
       <c r="J276" s="33"/>
@@ -30437,11 +30455,21 @@
       <c r="A277" s="78">
         <v>45847</v>
       </c>
-      <c r="B277" s="14"/>
-      <c r="C277" s="14"/>
-      <c r="D277" s="30"/>
-      <c r="E277" s="164"/>
-      <c r="F277" s="32"/>
+      <c r="B277" s="231" t="s">
+        <v>315</v>
+      </c>
+      <c r="C277" s="231" t="s">
+        <v>86</v>
+      </c>
+      <c r="D277" s="232">
+        <v>-0.0308</v>
+      </c>
+      <c r="E277" s="233">
+        <v>-0.0141</v>
+      </c>
+      <c r="F277" s="168">
+        <v>-0.0623</v>
+      </c>
       <c r="G277" s="33"/>
       <c r="H277" s="33"/>
       <c r="I277" s="33"/>
@@ -30460,10 +30488,18 @@
       <c r="A278" s="78">
         <v>45848</v>
       </c>
-      <c r="B278" s="14"/>
-      <c r="C278" s="14"/>
-      <c r="D278" s="30"/>
-      <c r="E278" s="164"/>
+      <c r="B278" s="231" t="s">
+        <v>316</v>
+      </c>
+      <c r="C278" s="231" t="s">
+        <v>88</v>
+      </c>
+      <c r="D278" s="232">
+        <v>0.0351</v>
+      </c>
+      <c r="E278" s="233">
+        <v>0.0725</v>
+      </c>
       <c r="F278" s="32"/>
       <c r="G278" s="33"/>
       <c r="H278" s="33"/>
@@ -31885,7 +31921,7 @@
         <v>45660</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C18" s="39">
         <v>-0.093</v>
@@ -31904,7 +31940,7 @@
         <v>1.1</v>
       </c>
       <c r="H18" s="43" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="I18" s="48"/>
       <c r="J18" s="48"/>
@@ -31927,7 +31963,7 @@
     <row r="19" s="2" customFormat="1" spans="1:16">
       <c r="A19" s="44"/>
       <c r="B19" s="45" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C19" s="46">
         <v>0.0047</v>
@@ -31947,7 +31983,7 @@
       <c r="L19" s="19"/>
       <c r="M19" s="19"/>
       <c r="N19" s="95" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O19" s="96"/>
       <c r="P19" s="97"/>
@@ -31957,7 +31993,7 @@
         <v>45663</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C20" s="39" t="s">
         <v>89</v>
@@ -31999,7 +32035,7 @@
         <v>45664</v>
       </c>
       <c r="B21" s="49" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C21" s="39">
         <v>-0.0163</v>
@@ -32008,7 +32044,7 @@
         <v>92</v>
       </c>
       <c r="E21" s="364" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F21" s="35">
         <v>0.1</v>
@@ -32039,7 +32075,7 @@
     <row r="22" s="2" customFormat="1" spans="1:16">
       <c r="A22" s="50"/>
       <c r="B22" s="51" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C22" s="46">
         <v>0.0314</v>
@@ -32059,7 +32095,7 @@
       <c r="L22" s="19"/>
       <c r="M22" s="19"/>
       <c r="N22" s="92" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="O22" s="93"/>
       <c r="P22" s="94"/>
@@ -32069,7 +32105,7 @@
         <v>45665</v>
       </c>
       <c r="B23" s="51" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C23" s="46">
         <v>0.0291</v>
@@ -32098,7 +32134,7 @@
         <v>9</v>
       </c>
       <c r="N23" s="92" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O23" s="93"/>
       <c r="P23" s="94"/>
@@ -32106,7 +32142,7 @@
     <row r="24" s="2" customFormat="1" spans="1:16">
       <c r="A24" s="55"/>
       <c r="B24" s="56" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C24" s="30">
         <v>-0.0677</v>
@@ -32126,7 +32162,7 @@
       <c r="L24" s="19"/>
       <c r="M24" s="19"/>
       <c r="N24" s="95" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O24" s="96"/>
       <c r="P24" s="97"/>
@@ -32134,7 +32170,7 @@
     <row r="25" s="2" customFormat="1" spans="1:16">
       <c r="A25" s="55"/>
       <c r="B25" s="56" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C25" s="30">
         <v>-0.0184</v>
@@ -32154,7 +32190,7 @@
       <c r="L25" s="19"/>
       <c r="M25" s="19"/>
       <c r="N25" s="95" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O25" s="96"/>
       <c r="P25" s="97"/>
@@ -32162,7 +32198,7 @@
     <row r="26" s="2" customFormat="1" spans="1:16">
       <c r="A26" s="55"/>
       <c r="B26" s="56" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C26" s="30">
         <v>0.0166</v>
@@ -32182,7 +32218,7 @@
       <c r="L26" s="19"/>
       <c r="M26" s="19"/>
       <c r="N26" s="95" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O26" s="96"/>
       <c r="P26" s="97"/>
@@ -32190,7 +32226,7 @@
     <row r="27" s="2" customFormat="1" spans="1:16">
       <c r="A27" s="57"/>
       <c r="B27" s="56" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C27" s="30">
         <v>-0.0383</v>
@@ -32210,7 +32246,7 @@
       <c r="L27" s="19"/>
       <c r="M27" s="19"/>
       <c r="N27" s="95" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O27" s="96"/>
       <c r="P27" s="97"/>
@@ -32220,7 +32256,7 @@
         <v>45666</v>
       </c>
       <c r="B28" s="58" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C28" s="30"/>
       <c r="D28" s="31"/>
@@ -32249,7 +32285,7 @@
     <row r="29" s="2" customFormat="1" spans="1:16">
       <c r="A29" s="55"/>
       <c r="B29" s="59" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C29" s="42">
         <v>-0.0222</v>
@@ -32267,7 +32303,7 @@
       <c r="L29" s="19"/>
       <c r="M29" s="19"/>
       <c r="N29" s="95" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O29" s="96"/>
       <c r="P29" s="97"/>
@@ -32275,7 +32311,7 @@
     <row r="30" s="2" customFormat="1" spans="1:16">
       <c r="A30" s="57"/>
       <c r="B30" s="58" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C30" s="42"/>
       <c r="D30" s="60"/>
@@ -32297,7 +32333,7 @@
         <v>45667</v>
       </c>
       <c r="B31" s="59" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C31" s="42">
         <v>-0.0209</v>
@@ -32324,7 +32360,7 @@
         <v>52</v>
       </c>
       <c r="N31" s="92" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="O31" s="93"/>
       <c r="P31" s="94"/>
@@ -32332,7 +32368,7 @@
     <row r="32" s="2" customFormat="1" spans="1:16">
       <c r="A32" s="55"/>
       <c r="B32" s="49" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C32" s="39">
         <v>-0.019</v>
@@ -32356,10 +32392,10 @@
     <row r="33" s="2" customFormat="1" spans="1:16">
       <c r="A33" s="55"/>
       <c r="B33" s="49" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C33" s="362" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D33" s="40" t="s">
         <v>89</v>
@@ -32376,7 +32412,7 @@
       <c r="L33" s="19"/>
       <c r="M33" s="19"/>
       <c r="N33" s="92" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="O33" s="93"/>
       <c r="P33" s="94"/>
@@ -32384,7 +32420,7 @@
     <row r="34" s="2" customFormat="1" spans="1:16">
       <c r="A34" s="57"/>
       <c r="B34" s="49" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C34" s="39">
         <v>0.0845</v>
@@ -32404,7 +32440,7 @@
       <c r="L34" s="19"/>
       <c r="M34" s="19"/>
       <c r="N34" s="92" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="O34" s="93"/>
       <c r="P34" s="94"/>
@@ -32414,7 +32450,7 @@
         <v>45670</v>
       </c>
       <c r="B35" s="49" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C35" s="39">
         <v>-0.09</v>
@@ -32454,7 +32490,7 @@
     <row r="36" s="2" customFormat="1" spans="1:16">
       <c r="A36" s="29"/>
       <c r="B36" s="49" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C36" s="39">
         <v>-0.0876</v>
@@ -32508,7 +32544,7 @@
         <v>45671</v>
       </c>
       <c r="B38" s="59" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C38" s="42" t="s">
         <v>89</v>
@@ -32548,7 +32584,7 @@
     <row r="39" s="2" customFormat="1" spans="1:16">
       <c r="A39" s="29"/>
       <c r="B39" s="59" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C39" s="42">
         <v>-0.0918</v>
@@ -32605,7 +32641,7 @@
         <v>45673</v>
       </c>
       <c r="B41" s="68" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C41" s="69">
         <v>0.0518</v>
@@ -32642,7 +32678,7 @@
         <v>45674</v>
       </c>
       <c r="B42" s="68" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C42" s="69">
         <v>-0.015</v>
@@ -32679,7 +32715,7 @@
         <v>45677</v>
       </c>
       <c r="B43" s="72" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C43" s="73">
         <v>-4.04</v>
@@ -32740,7 +32776,7 @@
     <row r="45" s="2" customFormat="1" spans="1:16">
       <c r="A45" s="71"/>
       <c r="B45" s="14" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C45" s="30">
         <v>-0.0908</v>
@@ -32826,7 +32862,7 @@
         <v>45680</v>
       </c>
       <c r="B48" s="38" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C48" s="39">
         <v>-0.0647</v>
@@ -32835,7 +32871,7 @@
         <v>92</v>
       </c>
       <c r="E48" s="364" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F48" s="35">
         <v>0.1</v>
@@ -32868,7 +32904,7 @@
         <v>45681</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C49" s="30"/>
       <c r="D49" s="31"/>
@@ -32897,7 +32933,7 @@
     <row r="50" s="2" customFormat="1" spans="1:16">
       <c r="A50" s="57"/>
       <c r="B50" s="14" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C50" s="30"/>
       <c r="D50" s="31"/>
@@ -32919,13 +32955,13 @@
         <v>45684</v>
       </c>
       <c r="B51" s="38" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C51" s="39" t="s">
         <v>89</v>
       </c>
       <c r="D51" s="40" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E51" s="41">
         <v>-0.0136</v>
@@ -32967,7 +33003,7 @@
       <c r="F52" s="33"/>
       <c r="G52" s="33"/>
       <c r="H52" s="77" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="I52" s="77"/>
       <c r="J52" s="77"/>
@@ -32992,7 +33028,7 @@
         <v>45694</v>
       </c>
       <c r="B53" s="72" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C53" s="42"/>
       <c r="D53" s="60"/>
@@ -33083,7 +33119,7 @@
         <v>45699</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C56" s="30"/>
       <c r="D56" s="31"/>
@@ -33114,7 +33150,7 @@
         <v>45700</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C57" s="30"/>
       <c r="D57" s="31"/>
@@ -33145,7 +33181,7 @@
         <v>45701</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C58" s="30"/>
       <c r="D58" s="31"/>
@@ -33174,7 +33210,7 @@
     <row r="59" spans="1:16">
       <c r="A59" s="80"/>
       <c r="B59" s="14" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C59" s="30"/>
       <c r="D59" s="31"/>
@@ -33194,7 +33230,7 @@
     <row r="60" spans="1:16">
       <c r="A60" s="81"/>
       <c r="B60" s="14" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C60" s="30"/>
       <c r="D60" s="31"/>
@@ -33216,7 +33252,7 @@
         <v>45702</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C61" s="30"/>
       <c r="D61" s="31"/>
@@ -33245,7 +33281,7 @@
     <row r="62" spans="1:16">
       <c r="A62" s="76"/>
       <c r="B62" s="14" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C62" s="30"/>
       <c r="D62" s="31"/>
@@ -33267,7 +33303,7 @@
         <v>45705</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C63" s="30"/>
       <c r="D63" s="31"/>
@@ -33329,7 +33365,7 @@
         <v>45707</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C65" s="30"/>
       <c r="D65" s="31"/>
@@ -33360,7 +33396,7 @@
         <v>45708</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C66" s="30"/>
       <c r="D66" s="31"/>
@@ -33389,7 +33425,7 @@
     <row r="67" spans="1:16">
       <c r="A67" s="103"/>
       <c r="B67" s="14" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C67" s="30"/>
       <c r="D67" s="31"/>
@@ -33425,7 +33461,7 @@
         <v>45709</v>
       </c>
       <c r="B69" s="14" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C69" s="30"/>
       <c r="D69" s="31"/>
@@ -33454,7 +33490,7 @@
     <row r="70" ht="16.25" spans="1:16">
       <c r="A70" s="107"/>
       <c r="B70" s="68" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C70" s="69"/>
       <c r="D70" s="108"/>
@@ -33476,7 +33512,7 @@
         <v>45712</v>
       </c>
       <c r="B71" s="68" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C71" s="69"/>
       <c r="D71" s="108"/>
@@ -33508,7 +33544,7 @@
     <row r="72" ht="16.25" spans="1:16">
       <c r="A72" s="103"/>
       <c r="B72" s="72" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C72" s="42"/>
       <c r="D72" s="111"/>
@@ -33528,7 +33564,7 @@
     <row r="73" spans="1:16">
       <c r="A73" s="105"/>
       <c r="B73" s="14" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C73" s="30"/>
       <c r="D73" s="113"/>
@@ -33550,7 +33586,7 @@
         <v>45713</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C74" s="30"/>
       <c r="D74" s="31"/>
@@ -33612,7 +33648,7 @@
         <v>45715</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C76" s="30"/>
       <c r="D76" s="31"/>
@@ -33672,7 +33708,7 @@
     <row r="78" spans="1:16">
       <c r="A78" s="117"/>
       <c r="B78" s="14" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C78" s="30"/>
       <c r="D78" s="31"/>
@@ -33717,7 +33753,7 @@
         <v>45720</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C80" s="30"/>
       <c r="D80" s="31"/>
@@ -33734,7 +33770,7 @@
     <row r="81" spans="1:16">
       <c r="A81" s="105"/>
       <c r="B81" s="72" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C81" s="42">
         <v>-0.084</v>
@@ -33825,7 +33861,7 @@
         <v>45723</v>
       </c>
       <c r="B84" s="14" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C84" s="30"/>
       <c r="D84" s="31"/>
@@ -33853,7 +33889,7 @@
         <v>45726</v>
       </c>
       <c r="B85" s="14" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C85" s="30"/>
       <c r="D85" s="31"/>
@@ -33879,7 +33915,7 @@
     <row r="86" spans="1:16">
       <c r="A86" s="103"/>
       <c r="B86" s="14" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C86" s="30"/>
       <c r="D86" s="31"/>
@@ -33896,7 +33932,7 @@
     <row r="87" spans="1:16">
       <c r="A87" s="105"/>
       <c r="B87" s="14" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C87" s="30"/>
       <c r="D87" s="31"/>
@@ -33915,7 +33951,7 @@
         <v>45727</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C88" s="30"/>
       <c r="D88" s="31"/>
@@ -33941,7 +33977,7 @@
     <row r="89" spans="1:16">
       <c r="A89" s="103"/>
       <c r="B89" s="14" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C89" s="30"/>
       <c r="D89" s="31"/>
@@ -33958,7 +33994,7 @@
     <row r="90" spans="1:16">
       <c r="A90" s="105"/>
       <c r="B90" s="14" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C90" s="30"/>
       <c r="D90" s="31"/>
@@ -34046,7 +34082,7 @@
     <row r="94" spans="1:16">
       <c r="A94" s="105"/>
       <c r="B94" s="14" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C94" s="30"/>
       <c r="D94" s="31"/>
@@ -34065,7 +34101,7 @@
         <v>45730</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C95" s="30"/>
       <c r="D95" s="31"/>
@@ -34145,7 +34181,7 @@
         <v>45735</v>
       </c>
       <c r="B98" s="14" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C98" s="30"/>
       <c r="D98" s="31"/>
@@ -34171,7 +34207,7 @@
     <row r="99" spans="1:16">
       <c r="A99" s="105"/>
       <c r="B99" s="14" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C99" s="30"/>
       <c r="D99" s="31"/>
@@ -34216,7 +34252,7 @@
         <v>45737</v>
       </c>
       <c r="B101" s="14" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C101" s="30"/>
       <c r="D101" s="31"/>
@@ -34242,7 +34278,7 @@
     <row r="102" spans="1:16">
       <c r="A102" s="119"/>
       <c r="B102" s="14" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C102" s="30"/>
       <c r="D102" s="31"/>
@@ -34287,7 +34323,7 @@
     <row r="104" spans="1:16">
       <c r="A104" s="103"/>
       <c r="B104" s="14" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C104" s="30"/>
       <c r="D104" s="31"/>
@@ -34304,7 +34340,7 @@
     <row r="105" spans="1:16">
       <c r="A105" s="105"/>
       <c r="B105" s="14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C105" s="30"/>
       <c r="D105" s="31"/>
@@ -34375,7 +34411,7 @@
         <v>45743</v>
       </c>
       <c r="B108" s="14" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C108" s="30"/>
       <c r="D108" s="31"/>
@@ -34429,7 +34465,7 @@
         <v>45747</v>
       </c>
       <c r="B110" s="14" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C110" s="30"/>
       <c r="D110" s="31"/>
@@ -34457,7 +34493,7 @@
         <v>45748</v>
       </c>
       <c r="B111" s="14" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C111" s="30"/>
       <c r="D111" s="31"/>
@@ -34511,7 +34547,7 @@
         <v>45750</v>
       </c>
       <c r="B113" s="14" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C113" s="30"/>
       <c r="D113" s="31"/>
@@ -34539,7 +34575,7 @@
         <v>45754</v>
       </c>
       <c r="B114" s="14" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C114" s="30"/>
       <c r="D114" s="31"/>
@@ -34575,7 +34611,7 @@
         <v>45755</v>
       </c>
       <c r="B116" s="14" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C116" s="30"/>
       <c r="D116" s="31"/>
@@ -34592,7 +34628,7 @@
     <row r="117" spans="1:16">
       <c r="A117" s="105"/>
       <c r="B117" s="14" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C117" s="30"/>
       <c r="D117" s="31"/>
@@ -34611,7 +34647,7 @@
         <v>45756</v>
       </c>
       <c r="B118" s="14" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C118" s="30"/>
       <c r="D118" s="31"/>
@@ -34630,7 +34666,7 @@
         <v>45757</v>
       </c>
       <c r="B119" s="14" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C119" s="30"/>
       <c r="D119" s="31"/>
@@ -34647,7 +34683,7 @@
     <row r="120" spans="1:16">
       <c r="A120" s="103"/>
       <c r="B120" s="14" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C120" s="30"/>
       <c r="D120" s="31"/>
@@ -34664,7 +34700,7 @@
     <row r="121" spans="1:16">
       <c r="A121" s="105"/>
       <c r="B121" s="14" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C121" s="30"/>
       <c r="D121" s="31"/>
@@ -35032,192 +35068,192 @@
   <sheetData>
     <row r="21" spans="11:11">
       <c r="K21" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="22" spans="11:11">
       <c r="K22" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="54" spans="5:5">
       <c r="E54" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="55" spans="5:5">
       <c r="E55" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="56" spans="5:5">
       <c r="E56" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="57" spans="5:5">
       <c r="E57" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="58" spans="5:5">
       <c r="E58" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="59" spans="5:5">
       <c r="E59" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="60" spans="5:5">
       <c r="E60" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="61" spans="5:5">
       <c r="E61" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="62" spans="5:5">
       <c r="E62" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="63" spans="5:5">
       <c r="E63" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="64" spans="5:5">
       <c r="E64" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="65" spans="5:5">
       <c r="E65" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="66" spans="5:5">
       <c r="E66" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="67" spans="5:5">
       <c r="E67" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="68" spans="5:5">
       <c r="E68" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="69" spans="5:5">
       <c r="E69" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="70" spans="5:5">
       <c r="E70" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="71" spans="5:5">
       <c r="E71" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="72" spans="5:5">
       <c r="E72" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="73" spans="5:5">
       <c r="E73" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="74" spans="5:5">
       <c r="E74" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="75" spans="5:5">
       <c r="E75" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="76" spans="5:5">
       <c r="E76" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="77" spans="5:5">
       <c r="E77" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="78" spans="5:5">
       <c r="E78" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="79" spans="5:5">
       <c r="E79" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="80" spans="5:5">
       <c r="E80" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="81" spans="5:5">
       <c r="E81" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="82" spans="5:5">
       <c r="E82" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="83" spans="5:5">
       <c r="E83" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="84" spans="5:5">
       <c r="E84" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="85" spans="5:5">
       <c r="E85" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="86" spans="5:5">
       <c r="E86" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="87" spans="5:5">
       <c r="E87" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="88" spans="5:5">
       <c r="E88" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="89" spans="5:5">
       <c r="E89" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>
